--- a/docs/quality/Defect Register/Defect Register v0.6.xlsx
+++ b/docs/quality/Defect Register/Defect Register v0.6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\SEN381\Repo\Ticketing-System\docs\quality\Defect Register\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA50AF3-CDF7-459B-86BB-7E839762B4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5401FC46-B2FF-4E67-9245-F37E2171B621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="220">
   <si>
     <t>Defect Register</t>
   </si>
@@ -272,12 +272,6 @@
     <t>A client retrying after a timeout cannot treat the retry as the original response and has to handle a second response shape.</t>
   </si>
   <si>
-    <t>Pending, separate PR</t>
-  </si>
-  <si>
-    <t>Pending: the same tests re-run unchanged after the fix</t>
-  </si>
-  <si>
     <t>Open. Not a release block under the scale (S3). No second history entry is written on a replay.</t>
   </si>
   <si>
@@ -344,9 +338,6 @@
     <t>A client cannot tell an authorisation refusal from a validation failure, so it cannot show the right message or decide whether retrying is sensible. No user impact today because there is no client, but it is a contract defect against DEC-015 and it will mislead the one we are about to build.</t>
   </si>
   <si>
-    <t>Pending: the same tests re-run unchanged after the fix (wrongRoleTransition.integration.test.js)</t>
-  </si>
-  <si>
     <t>Not blocking. Fix with DEF-007 to DEF-010 in the same PR, same file, same decision.</t>
   </si>
   <si>
@@ -548,9 +539,6 @@
     <t>Robert</t>
   </si>
   <si>
-    <t>M3 brief §12: "Maintain a simple defect record: defect -&gt; severity/impact -&gt; status -&gt; fix -&gt; regression evidence where corrected." §15: "Known defects | Open/closed | Business impact | Block or residual risk". Each row has a stable DEF identifier the RTM Defect/Status column can cite. Identifiers are never reused or renumbered; a closed defect stays in the register. | Version 0.6 (17/10/2026, M4 final pass, R. van der Merwe). Adds DEF-021 (staging did not serve the client until the Nginx site file was corrected on 15/10/2026; recorded at M3 only in the deploy record, and entered here so the register is complete), raised by E. Lindsay and allocated by R. van der Merwe. Adds columns P (Final status, M4: Fixed, Open or No longer relevant) and Q (the evidence, or the limitation and its consequence). DEF-006 is fixed by DEC-003 v0.5, and its J to M cells are completed. DEF-019's L and M cells cite PR #123. DEF-007 to DEF-012 are on E. Lindsay's M4 fix list; their P and Q cells are completed from his v4.0-M4-rc evidence (UTC) before this version merges. No other existing cell changes. Version 0.5 (15/10/2026). Adds DEF-019 (two test titles cite the wrong requirement), raised by E. Lindsay, and DEF-020 (the staging MONGODB_URI named no database, so the application used the default test database), raised by R. van der Merwe. Closes DEF-014, DEF-015 and DEF-017: their unique indexes were provisioned and confirmed on the test cluster (PR #102) and the staging cluster (PR #111); closure text by R. van der Merwe, entered by E. Lindsay. DEF-006 records the one-off drop of the test database on 14/10/2026. DEF-001 to DEF-005, DEF-007 to DEF-013, DEF-016 and DEF-018 unchanged. Version 0.4 (14/10/2026). Adds DEF-018 (an unexplained npm test failure in the PR #98 build: 3 failures, test names not captured), raised by R. van der Merwe. DEF-001 to DEF-017 unchanged. Version 0.3 (12/10/2026). Adds DEF-017 (the unique index on users.email is absent on the test cluster; FR-1.1 relies on it alone), raised by E. Lindsay; DEF-014 and DEF-015 cell E updated with the observed index absence from the test-cluster listing. DEF-001 to DEF-016 otherwise unchanged. Version 0.2 (12/10/2026). Adds DEF-005 to DEF-016: DEF-007 to DEF-010, DEF-014, and DEF-015 from M3 integration testing (R. van der Merwe); DEF-005, DEF-006, DEF-011 to DEF-013, and DEF-016 raised by E. Lindsay. DEF-001 to DEF-004 unchanged. Version 0.1 (11/10/2026). Register created with DEF-001 to DEF-004.</t>
-  </si>
-  <si>
     <t>DEF-021</t>
   </si>
   <si>
@@ -608,21 +596,6 @@
     <t>The record now matches the practice: DEC-003 v0.5's Test row (PR #134). Residual: the test cluster is still not isolated between runs, so cluster-based evidence carries that caveat. From PR #122 the CI integration cases run on a throwaway database.</t>
   </si>
   <si>
-    <t>[Sunday RC check]</t>
-  </si>
-  <si>
-    <t>On E. Lindsay's M4 fix list. To be completed from his v4.0-M4-rc evidence (UTC): the fix's commit, the CI integration job's result (PR #122), and Fixed or Open with its limitation.</t>
-  </si>
-  <si>
-    <t>On E. Lindsay's M4 fix list. To be completed from his v4.0-M4-rc evidence (UTC): the fix's commit, the CI integration job's result (PR #122), and Fixed or Open with its limitation. S2: if it is not fixed, it must be named in the go-live decision.</t>
-  </si>
-  <si>
-    <t>On E. Lindsay's M4 fix list. To be completed from his v4.0-M4-rc evidence (UTC): the fix's commit, the CI integration result, and whether E2E-2b's expected-failure mark is removed.</t>
-  </si>
-  <si>
-    <t>On E. Lindsay's M4 fix list. To be completed from his v4.0-M4-rc evidence (UTC): the fix's commit, the test that shows a malformed id now gets 400, and Fixed or Open.</t>
-  </si>
-  <si>
     <t>Limitation: the cause is unknown and the failure message was never captured. There was no recurrence in CI from 13/10/2026 to 17/10/2026: in 104 workflow runs the Build and test job failed only once, in run 38357191208, the deliberate GATE-01 layer-check demonstration. Absence of recurrence is not a fix. Consequence: the test of the session cookie's security attributes (DEC-018 §3) passes, with this caveat named in the release evidence. Future work: run with a reporter that captures test names and messages.</t>
   </si>
   <si>
@@ -638,12 +611,6 @@
     <t>Limitation: three failures with names not captured, and the cause unknown. There was no recurrence in CI from 13/10/2026 to 17/10/2026 (104 workflow runs; Build and test failed only in the deliberate GATE-01 run 38357191208). Consequence: as for DEF-013 and DEF-016, which it may be the same as. Future work: capture names and messages if it recurs, and never re-run until green.</t>
   </si>
   <si>
-    <t>Fixed [Sunday RC check: PR #123 merged before v4.0-M4-rc]</t>
-  </si>
-  <si>
-    <t>Both titles corrected in PR #123 (6482ee1), assertions unchanged, suite 200 / 192 / 0 fail at 404a471. Final once #123 is in v4.0-M4-rc.</t>
-  </si>
-  <si>
     <t>Fixed on staging at 16:12:28 UTC on 15/10/2026. The load run and the smoke test that followed used the civicconnect database (PR #111), and the perf scripts refuse a URI without the database name (PR #110). Residual, still open: src/config.js does not refuse such a URI, and /health does not show which database it uses. DEC-003 v0.5 now states the rule, and the Health check row states what /health does not prove.</t>
   </si>
   <si>
@@ -663,6 +630,72 @@
   </si>
   <si>
     <t>tests/requestStatus.test.js now cites "proposed transition model, OI-15", and tests/statusTransitionService.test.js cites AC-FR-6.3. Full suite at 404a471: 200 tests, 192 pass, 0 fail, 8 skipped (PR #123). RTM v0.11 cites the corrected titles.</t>
+  </si>
+  <si>
+    <t>M3 brief §12: "Maintain a simple defect record: defect -&gt; severity/impact -&gt; status -&gt; fix -&gt; regression evidence where corrected." §15: "Known defects | Open/closed | Business impact | Block or residual risk". Each row has a stable DEF identifier the RTM Defect/Status column can cite. Identifiers are never reused or renumbered; a closed defect stays in the register. | Version 0.6 (17/10/2026, M4 final pass, R. van der Merwe). Adds DEF-021 (staging did not serve the client until the Nginx site file was corrected on 15/10/2026; recorded at M3 only in the deploy record, and entered here so the register is complete), raised by E. Lindsay and allocated by R. van der Merwe. Adds columns P (Final status, M4: Fixed, Open or No longer relevant) and Q (the evidence, or the limitation and its consequence). DEF-006 is fixed by DEC-003 v0.5, and its J to M cells are completed. DEF-019's L and M cells cite PR #123. DEF-007 to DEF-012 were on E. Lindsay's M4 fix list; their J to Q cells were completed on 18/10/2026 from the v4.0-M4-rc evidence, and DEF-019 is closed (PR #123 is in the release candidate). No other existing cell changes. Version 0.5 (15/10/2026). Adds DEF-019 (two test titles cite the wrong requirement), raised by E. Lindsay, and DEF-020 (the staging MONGODB_URI named no database, so the application used the default test database), raised by R. van der Merwe. Closes DEF-014, DEF-015 and DEF-017: their unique indexes were provisioned and confirmed on the test cluster (PR #102) and the staging cluster (PR #111); closure text by R. van der Merwe, entered by E. Lindsay. DEF-006 records the one-off drop of the test database on 14/10/2026. DEF-001 to DEF-005, DEF-007 to DEF-013, DEF-016 and DEF-018 unchanged. Version 0.4 (14/10/2026). Adds DEF-018 (an unexplained npm test failure in the PR #98 build: 3 failures, test names not captured), raised by R. van der Merwe. DEF-001 to DEF-017 unchanged. Version 0.3 (12/10/2026). Adds DEF-017 (the unique index on users.email is absent on the test cluster; FR-1.1 relies on it alone), raised by E. Lindsay; DEF-014 and DEF-015 cell E updated with the observed index absence from the test-cluster listing. DEF-001 to DEF-016 otherwise unchanged. Version 0.2 (12/10/2026). Adds DEF-005 to DEF-016: DEF-007 to DEF-010, DEF-014, and DEF-015 from M3 integration testing (R. van der Merwe); DEF-005, DEF-006, DEF-011 to DEF-013, and DEF-016 raised by E. Lindsay. DEF-001 to DEF-004 unchanged. Version 0.1 (11/10/2026). Register created with DEF-001 to DEF-004.</t>
+  </si>
+  <si>
+    <t>Replay returns the original status and body with Idempotent-Replayed: true (DEC-015 §3).</t>
+  </si>
+  <si>
+    <t>PR #136, commits 804138f and e973a9d</t>
+  </si>
+  <si>
+    <t>Integration cases 2b re-run unchanged: 40 of 40 at the frozen build 6408ab7 (docs/evidence/M4-build/API_integration_run_2026-10-17_run3_frozen_build.txt) and in CI on dev (run 39079571516, MongoDB 8.0 replica set). Negative verifications NV-134 to NV-138 and NV-158.</t>
+  </si>
+  <si>
+    <t>Fixed at M4 in PR #136, inside v4.0-M4-rc (f1eb7af, tested build 6408ab7). Evidence: Integration cases 2b re-run unchanged: 40 of 40 at the frozen build 6408ab7 (docs/evidence/M4-build/API_integration_run_2026-10-17_run3_frozen_build.txt) and in CI on dev (run 39079571516, MongoDB 8.0 replica set). Negative verifications NV-134 to NV-138 and NV-158.</t>
+  </si>
+  <si>
+    <t>The 412 problem body carries the current ETag (DEC-015 §2).</t>
+  </si>
+  <si>
+    <t>Integration case (ifMatchConflict) re-run unchanged: 40 of 40 at 6408ab7 and in CI run 39079571516. NV-134 to NV-138, NV-158.</t>
+  </si>
+  <si>
+    <t>Fixed at M4 in PR #136, inside v4.0-M4-rc (f1eb7af, tested build 6408ab7). Evidence: Integration case (ifMatchConflict) re-run unchanged: 40 of 40 at 6408ab7 and in CI run 39079571516. NV-134 to NV-138, NV-158.</t>
+  </si>
+  <si>
+    <t>The fingerprint covers method, path and the canonical JSON body, so a key used on another request or with reordered members is handled as DEC-015 §3 requires.</t>
+  </si>
+  <si>
+    <t>Integration cases 2d and 2e re-run unchanged: 40 of 40 at 6408ab7 and in CI run 39079571516. NV-134 to NV-138, NV-158.</t>
+  </si>
+  <si>
+    <t>Fixed at M4 in PR #136, inside v4.0-M4-rc (f1eb7af, tested build 6408ab7). Evidence: Integration cases 2d and 2e re-run unchanged: 40 of 40 at 6408ab7 and in CI run 39079571516. NV-134 to NV-138, NV-158.</t>
+  </si>
+  <si>
+    <t>The problem type is idempotency-key-reused (DEC-015 §3), in the code and the contract.</t>
+  </si>
+  <si>
+    <t>Integration case 2c re-run unchanged: 40 of 40 at 6408ab7 and in CI run 39079571516. NV-134 to NV-138, NV-158.</t>
+  </si>
+  <si>
+    <t>Fixed at M4 in PR #136, inside v4.0-M4-rc (f1eb7af, tested build 6408ab7). Evidence: Integration case 2c re-run unchanged: 40 of 40 at 6408ab7 and in CI run 39079571516. NV-134 to NV-138, NV-158.</t>
+  </si>
+  <si>
+    <t>A role not permitted for the transition is refused with 403 (DEC-015 §4); a domain-rule refusal stays 422.</t>
+  </si>
+  <si>
+    <t>wrongRoleTransition.integration.test.js re-run unchanged: 40 of 40 at 6408ab7 and in CI run 39079571516; E2E-2b passes in four browsers (56 of 56 at 6408ab7). NV-134 to NV-138, NV-158.</t>
+  </si>
+  <si>
+    <t>Fixed at M4 in PR #136, inside v4.0-M4-rc (f1eb7af, tested build 6408ab7). Evidence: wrongRoleTransition.integration.test.js re-run unchanged: 40 of 40 at 6408ab7 and in CI run 39079571516; E2E-2b passes in four browsers (56 of 56 at 6408ab7). NV-134 to NV-138, NV-158.</t>
+  </si>
+  <si>
+    <t>A malformed request id is refused with 400 in the repository, before any read, so every route that reads a request by id is covered (src/repositories/requestRepository.js).</t>
+  </si>
+  <si>
+    <t>PR #136, commit 804138f</t>
+  </si>
+  <si>
+    <t>NV-139: the guard line broken, the test seen to fail, the line restored. Unit suite at 6408ab7.</t>
+  </si>
+  <si>
+    <t>Fixed at M4 in PR #136, inside v4.0-M4-rc (f1eb7af, tested build 6408ab7). Evidence: NV-139: the guard line broken, the test seen to fail, the line restored. Unit suite at 6408ab7.</t>
+  </si>
+  <si>
+    <t>Both titles corrected in PR #123 (6482ee1), assertions unchanged, suite 200 / 192 / 0 fail at 404a471. PR #123 merged before the release candidate and is inside v4.0-M4-rc.</t>
   </si>
 </sst>
 </file>
@@ -1161,7 +1194,7 @@
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
@@ -1239,10 +1272,10 @@
         <v>20</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1290,10 +1323,10 @@
         <v>33</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1341,10 +1374,10 @@
         <v>33</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1392,10 +1425,10 @@
         <v>33</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1443,10 +1476,10 @@
         <v>33</v>
       </c>
       <c r="P14" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q14" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="15" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1497,7 +1530,7 @@
         <v>66</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1512,7 +1545,7 @@
         <v>33</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>70</v>
@@ -1530,13 +1563,13 @@
         <v>28</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="N16" s="5" t="s">
         <v>72</v>
@@ -1545,10 +1578,10 @@
         <v>33</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1578,33 +1611,33 @@
         <v>27</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="K17" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="N17" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="L17" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="M17" s="5" t="s">
+      <c r="O17" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="N17" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="P17" s="5" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="0"/>
@@ -1614,48 +1647,48 @@
         <v>74</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="M18" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="O18" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="P18" s="5" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="0"/>
@@ -1665,48 +1698,48 @@
         <v>74</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>78</v>
+        <v>206</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="M19" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="O19" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="N19" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="P19" s="5" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="0"/>
@@ -1716,48 +1749,48 @@
         <v>74</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="M20" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="O20" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="N20" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="O20" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="P20" s="5" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C21" s="4">
         <f t="shared" si="0"/>
@@ -1767,48 +1800,48 @@
         <v>33</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>67</v>
+        <v>212</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>67</v>
+        <v>200</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O21" s="5" t="s">
         <v>33</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" si="0"/>
@@ -1818,48 +1851,48 @@
         <v>33</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>67</v>
+        <v>215</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>67</v>
+        <v>217</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O22" s="5" t="s">
         <v>33</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C23" s="4">
         <f t="shared" si="0"/>
@@ -1869,19 +1902,19 @@
         <v>33</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>66</v>
@@ -1893,10 +1926,10 @@
         <v>67</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="O23" s="5" t="s">
         <v>33</v>
@@ -1905,31 +1938,31 @@
         <v>66</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="0"/>
         <v>46307</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>27</v>
@@ -1938,49 +1971,49 @@
         <v>28</v>
       </c>
       <c r="K24" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="N24" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="N24" s="5" t="s">
-        <v>155</v>
       </c>
       <c r="O24" s="5" t="s">
         <v>33</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C25" s="4">
         <f t="shared" si="0"/>
         <v>46307</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>27</v>
@@ -1989,30 +2022,30 @@
         <v>28</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O25" s="5" t="s">
         <v>33</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="0"/>
@@ -2022,16 +2055,16 @@
         <v>33</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>27</v>
@@ -2040,16 +2073,16 @@
         <v>66</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L26" s="5" t="s">
         <v>67</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="O26" s="5" t="s">
         <v>33</v>
@@ -2058,12 +2091,12 @@
         <v>66</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="2:17" ht="174" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" si="0"/>
@@ -2073,16 +2106,16 @@
         <v>33</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>27</v>
@@ -2091,49 +2124,49 @@
         <v>28</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>33</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="2:17" ht="174" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C28" s="4">
         <f>DATE(2026,10,14)</f>
         <v>46309</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>27</v>
@@ -2142,7 +2175,7 @@
         <v>66</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>67</v>
@@ -2151,7 +2184,7 @@
         <v>67</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>33</v>
@@ -2160,82 +2193,82 @@
         <v>66</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="2:17" ht="174" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C29" s="4">
         <f>DATE(2026,10,15)</f>
         <v>46310</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>65</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>33</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="2:17" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C30" s="4">
         <f>DATE(2026,10,15)</f>
         <v>46310</v>
       </c>
       <c r="D30" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>27</v>
@@ -2244,48 +2277,48 @@
         <v>28</v>
       </c>
       <c r="K30" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="N30" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="L30" s="6" t="s">
+      <c r="O30" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="M30" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="N30" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>169</v>
-      </c>
       <c r="P30" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C31" s="4">
         <v>46312</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>27</v>
@@ -2294,25 +2327,25 @@
         <v>28</v>
       </c>
       <c r="K31" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="N31" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="O31" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="L31" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="M31" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="N31" s="6" t="s">
+      <c r="P31" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="O31" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="P31" s="6" t="s">
-        <v>183</v>
-      </c>
       <c r="Q31" s="6" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/docs/quality/Defect Register/Defect Register v0.6.xlsx
+++ b/docs/quality/Defect Register/Defect Register v0.6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\SEN381\Repo\Ticketing-System\docs\quality\Defect Register\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5401FC46-B2FF-4E67-9245-F37E2171B621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443AE430-7E4E-4CF1-93E8-960089DFF339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Defect Register" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Defect Register'!$B$10:$Q$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Defect Register'!$B$10:$Q$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="311">
   <si>
     <t>Defect Register</t>
   </si>
@@ -632,9 +632,6 @@
     <t>tests/requestStatus.test.js now cites "proposed transition model, OI-15", and tests/statusTransitionService.test.js cites AC-FR-6.3. Full suite at 404a471: 200 tests, 192 pass, 0 fail, 8 skipped (PR #123). RTM v0.11 cites the corrected titles.</t>
   </si>
   <si>
-    <t>M3 brief §12: "Maintain a simple defect record: defect -&gt; severity/impact -&gt; status -&gt; fix -&gt; regression evidence where corrected." §15: "Known defects | Open/closed | Business impact | Block or residual risk". Each row has a stable DEF identifier the RTM Defect/Status column can cite. Identifiers are never reused or renumbered; a closed defect stays in the register. | Version 0.6 (17/10/2026, M4 final pass, R. van der Merwe). Adds DEF-021 (staging did not serve the client until the Nginx site file was corrected on 15/10/2026; recorded at M3 only in the deploy record, and entered here so the register is complete), raised by E. Lindsay and allocated by R. van der Merwe. Adds columns P (Final status, M4: Fixed, Open or No longer relevant) and Q (the evidence, or the limitation and its consequence). DEF-006 is fixed by DEC-003 v0.5, and its J to M cells are completed. DEF-019's L and M cells cite PR #123. DEF-007 to DEF-012 were on E. Lindsay's M4 fix list; their J to Q cells were completed on 18/10/2026 from the v4.0-M4-rc evidence, and DEF-019 is closed (PR #123 is in the release candidate). No other existing cell changes. Version 0.5 (15/10/2026). Adds DEF-019 (two test titles cite the wrong requirement), raised by E. Lindsay, and DEF-020 (the staging MONGODB_URI named no database, so the application used the default test database), raised by R. van der Merwe. Closes DEF-014, DEF-015 and DEF-017: their unique indexes were provisioned and confirmed on the test cluster (PR #102) and the staging cluster (PR #111); closure text by R. van der Merwe, entered by E. Lindsay. DEF-006 records the one-off drop of the test database on 14/10/2026. DEF-001 to DEF-005, DEF-007 to DEF-013, DEF-016 and DEF-018 unchanged. Version 0.4 (14/10/2026). Adds DEF-018 (an unexplained npm test failure in the PR #98 build: 3 failures, test names not captured), raised by R. van der Merwe. DEF-001 to DEF-017 unchanged. Version 0.3 (12/10/2026). Adds DEF-017 (the unique index on users.email is absent on the test cluster; FR-1.1 relies on it alone), raised by E. Lindsay; DEF-014 and DEF-015 cell E updated with the observed index absence from the test-cluster listing. DEF-001 to DEF-016 otherwise unchanged. Version 0.2 (12/10/2026). Adds DEF-005 to DEF-016: DEF-007 to DEF-010, DEF-014, and DEF-015 from M3 integration testing (R. van der Merwe); DEF-005, DEF-006, DEF-011 to DEF-013, and DEF-016 raised by E. Lindsay. DEF-001 to DEF-004 unchanged. Version 0.1 (11/10/2026). Register created with DEF-001 to DEF-004.</t>
-  </si>
-  <si>
     <t>Replay returns the original status and body with Idempotent-Replayed: true (DEC-015 §3).</t>
   </si>
   <si>
@@ -696,6 +693,282 @@
   </si>
   <si>
     <t>Both titles corrected in PR #123 (6482ee1), assertions unchanged, suite 200 / 192 / 0 fail at 404a471. PR #123 merged before the release candidate and is inside v4.0-M4-rc.</t>
+  </si>
+  <si>
+    <t>DEF-022</t>
+  </si>
+  <si>
+    <t>E. Lindsay, during the M4 integration of the build tracks, while planning the staging seed, 17/10/2026</t>
+  </si>
+  <si>
+    <t>The request reference sequence was kept per campus and year (counter _id 'request-ref:&lt;campusId&gt;:&lt;yyyy&gt;'), but Request.reference is unique across all requests (unique index reference_1) and the format CC-yyyy-nnnnnn carries no campus. A second campus would issue CC-2026-000001 again and its submission would be refused by the unique index. Every E2E fixture and every seed run creates a new synthetic campus.</t>
+  </si>
+  <si>
+    <t>FR-2.6, AC-FR-2.6, FR-2.1, DB-01 §3.8 (counters), src/repositories/counterRepository.js, src/services/requestSubmissionService.js, src/models/Counter.js</t>
+  </si>
+  <si>
+    <t>Submissions from a second campus would fail at the first reference already issued elsewhere. Uniqueness itself held (the database refused the duplicate), so no data was corrupted, but the submission journey would break for every campus after the first, including the E2E fixtures and the staging seed.</t>
+  </si>
+  <si>
+    <t>One reference sequence per UTC year (counter _id 'request-ref:&lt;yyyy&gt;'), incremented inside the submission transaction as before. Multi-campus operation is deferred (SCP-019), so a single sequence matches the campus-less reference.</t>
+  </si>
+  <si>
+    <t>Integration commit 7766eec on task/M4-final-product (decision D12)</t>
+  </si>
+  <si>
+    <t>tests/referenceSequence.test.js: two campuses in the same year get CC-2026-000001 and CC-2026-000002. NV-150: the campus put back into the key, the test failed, restored, SHA-256 identical. E2E-3 submitted through the UI on the test cluster (E2E run 1, 8cbc734, and the four-browser run, f26722d).</t>
+  </si>
+  <si>
+    <t>Closed. Residual: the sequence is global, so a future multi-campus design (SCP-019) must revisit the reference format.</t>
+  </si>
+  <si>
+    <t>Fixed before the M4 release candidate; regression test and NV-150 above; submissions shown on the test cluster in four browsers.</t>
+  </si>
+  <si>
+    <t>DEF-023</t>
+  </si>
+  <si>
+    <t>E. Lindsay, during the M4 integration of the build tracks, 17/10/2026</t>
+  </si>
+  <si>
+    <t>POST /api/v1/sessions for an account holding no role answered 500 instead of DEC-018 §5's identical 401: login reached primaryRole(), which throws when an actor holds no role.</t>
+  </si>
+  <si>
+    <t>DEC-018 §5, FR-1.2, FR-1.1, src/services/authService.js (login), src/domain/accessRules.js (primaryRole)</t>
+  </si>
+  <si>
+    <t>Such an account can only exist through a direct database write, because the User model requires a role (AC-FR-1.2). The 500 was distinguishable from the generic 401, so it revealed that the e-mail and password were valid; no data was disclosed.</t>
+  </si>
+  <si>
+    <t>Login refuses an account with no role on the same path as a revoked account: the password hash is checked first, then the same generic 401, so neither the response nor its timing distinguishes it.</t>
+  </si>
+  <si>
+    <t>Commit f26722d on task/M4-final-product</t>
+  </si>
+  <si>
+    <t>tests/app.test.js 'an account holding no role is refused with the same 401, not a 500': 401, no cookie, body identical to an unknown e-mail. NV-160: the role check removed, the test failed, restored, SHA-256 identical.</t>
+  </si>
+  <si>
+    <t>Closed. No residual.</t>
+  </si>
+  <si>
+    <t>Fixed before the M4 release candidate; regression test and NV-160 above.</t>
+  </si>
+  <si>
+    <t>DEF-024</t>
+  </si>
+  <si>
+    <t>E. Lindsay, local walkthrough of the M4 build on the test cluster, 17/10/2026</t>
+  </si>
+  <si>
+    <t>A per-viewer API response was reused from the browser cache after a user switch. GET /api/v1/requests/{id} carries ETag "v&lt;version&gt;", which depends only on the version, while the body differs per viewer; Express answered the browser's If-None-Match with 304 and no Cache-Control was sent, so the next user in the same browser was shown the previous user's view (seen as the Coordinator not offered Closed after a Technician, and the Security Officer shown no description after the Requester).</t>
+  </si>
+  <si>
+    <t>FR-1.5, AC-FR-1.5, AC-NFR-4.4, FR-6.6, DEC-015 §2, CON-007; src/app.js, every per-viewer /api response</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>On a shared browser the next user could be shown fields FR-1.5 restricts, from the previous user's cached response (for example a Security Officer's view of a security request shown to its requester). Staff were also shown the wrong permitted actions.</t>
+  </si>
+  <si>
+    <t>Every /api response carries Cache-Control: no-store and the API ignores conditional-GET request headers, so it never answers 304 (DEC-015 uses the ETag for If-Match only). The client also discards data loaded for the previous user when the signed-in user changes.</t>
+  </si>
+  <si>
+    <t>Commits 74287c6 (server) and 1704220 (client) on task/M4-final-product</t>
+  </si>
+  <si>
+    <t>tests/apiCaching.test.js failed before the fix (304 where 200 was expected) and passes after; NV-161. E2E-10 (one tab, users switching) passed in four browsers: E2E run after the section A fixes, 09e6e6a, 17:17:57-17:20:59 UTC 17/10/2026: 44 of 44 in Chromium, Chrome, Edge and Firefox (docs/evidence/M4-build/E2E_run_2026-10-17_sectionA_four_browsers.txt).</t>
+  </si>
+  <si>
+    <t>Closed. Residual: a browser that ignores Cache-Control could still store responses; none of the four tested did.</t>
+  </si>
+  <si>
+    <t>Fixed before the M4 release candidate; the regression evidence above.</t>
+  </si>
+  <si>
+    <t>DEF-025</t>
+  </si>
+  <si>
+    <t>User revocation (POST /api/v1/users/{id}/revocation) and category deactivation (POST /api/v1/categories/{id}/deactivation) were refused with 415 from the user interface: the client sent these writes without a body, and the server accepts a POST, PUT or PATCH only as application/json (DEC-015 §5).</t>
+  </si>
+  <si>
+    <t>FR-1.4, AC-FR-1.4, FR-9.1, AC-FR-9.1, DEC-015 §5; client/src/api.js</t>
+  </si>
+  <si>
+    <t>An Administrator could neither revoke access nor deactivate a category from the user interface; the revocation tested on 17/10/2026 did not take effect.</t>
+  </si>
+  <si>
+    <t>Every POST, PUT and PATCH from the client sends Content-Type application/json and a JSON body ({} when there is none).</t>
+  </si>
+  <si>
+    <t>Commit 1704220 on task/M4-final-product</t>
+  </si>
+  <si>
+    <t>E2E-7 revokes a user (listed as Revoked, the session ends, sign-in refused) and deactivates a category (no longer offered on New request): E2E run after the section A fixes, 09e6e6a, 17:17:57-17:20:59 UTC 17/10/2026: 44 of 44 in Chromium, Chrome, Edge and Firefox (docs/evidence/M4-build/E2E_run_2026-10-17_sectionA_four_browsers.txt).</t>
+  </si>
+  <si>
+    <t>DEF-026</t>
+  </si>
+  <si>
+    <t>A revoked user disappeared from the Administrator's Users list: GET /api/v1/users returned active users only.</t>
+  </si>
+  <si>
+    <t>FR-1.4, DEC-015 Addendum A (A2); src/services/userAdminService.js, client/src/screens/Admin.jsx</t>
+  </si>
+  <si>
+    <t>An Administrator could not see that an account had been revoked, or confirm a revocation.</t>
+  </si>
+  <si>
+    <t>For an Administrator the list includes revoked users with status and revokedAt, shown as 'Revoked on &lt;date&gt;' without role editing or a Revoke button; the assignment pool still excludes them.</t>
+  </si>
+  <si>
+    <t>tests/userListRevoked.test.js failed before the fix and passes after; NV-162. E2E-7: E2E run after the section A fixes, 09e6e6a, 17:17:57-17:20:59 UTC 17/10/2026: 44 of 44 in Chromium, Chrome, Edge and Firefox (docs/evidence/M4-build/E2E_run_2026-10-17_sectionA_four_browsers.txt).</t>
+  </si>
+  <si>
+    <t>DEF-027</t>
+  </si>
+  <si>
+    <t>A Security Officer was offered Accept on, and could be assigned, a non-security request in their categories, contrary to decision #10 (Security Officer for security-category requests only, Technician for the others).</t>
+  </si>
+  <si>
+    <t>FR-5.1, FR-5.2, FR-5.5, decision #10, OI-15; src/domain/accessRules.js (mayBeAssigned), client assign picker</t>
+  </si>
+  <si>
+    <t>A request could be owned by the wrong role; the Coordinator's picker could offer users the rule should exclude.</t>
+  </si>
+  <si>
+    <t>mayBeAssigned allows a Security Officer on security-category requests only and a Technician on the others, for assign, reassign and accept. The read carries permittedAssignment.assigneeRoles, derived from the same rule, and the picker offers only those roles.</t>
+  </si>
+  <si>
+    <t>Commits 74287c6 and 949cfdf on task/M4-final-product</t>
+  </si>
+  <si>
+    <t>tests/assignmentSecurityRule.test.js failed before the fix and passes after; NV-163; the pool agreement test, NV-168. E2E-8: E2E run after the section A fixes, 09e6e6a, 17:17:57-17:20:59 UTC 17/10/2026: 44 of 44 in Chromium, Chrome, Edge and Firefox (docs/evidence/M4-build/E2E_run_2026-10-17_sectionA_four_browsers.txt).</t>
+  </si>
+  <si>
+    <t>Closed. The rule is a team inference recorded under OI-15.</t>
+  </si>
+  <si>
+    <t>DEF-028</t>
+  </si>
+  <si>
+    <t>The Manager's Categories page did not show a category's current target resolution time: GET /api/v1/categories did not return targetResolutionHours, although PUT .../target succeeded.</t>
+  </si>
+  <si>
+    <t>FR-8.4, AC-FR-8.4, DEC-015 Addendum A (A1, A7); src/services/categoryService.js, client/src/screens/Admin.jsx</t>
+  </si>
+  <si>
+    <t>The Manager could set a target but not see or check it.</t>
+  </si>
+  <si>
+    <t>GET /api/v1/categories returns targetResolutionHours to the roles that may set or administer it (Manager, Administrator) and to no one else; the Categories page shows it. Addendum A row A1 updated.</t>
+  </si>
+  <si>
+    <t>tests/categoryTargetVisibility.test.js failed before the fix and passes after; NV-166.</t>
+  </si>
+  <si>
+    <t>DEF-029</t>
+  </si>
+  <si>
+    <t>The NFR-1.11 performance log named an operation whose error was raised after route matching as "POST /" (for example a 400, 401 or 403 from POST /api/v1/requests), because Express resets req.baseUrl when the error leaves the router.</t>
+  </si>
+  <si>
+    <t>NFR-1.11, AC-NFR-1.11, NFR-2.1 (the server-side timing reads this log); src/middleware/performanceLog.js, src/app.js</t>
+  </si>
+  <si>
+    <t>Refused and failed operations could not be attributed to their route in the log the NFR-2.1 check reads.</t>
+  </si>
+  <si>
+    <t>The mount path is recorded before each router and the log uses it, so every outcome names the real route pattern; an unmatched path keeps a fixed label.</t>
+  </si>
+  <si>
+    <t>Commit 74287c6 on task/M4-final-product</t>
+  </si>
+  <si>
+    <t>tests/performanceLogRoute.test.js failed before the fix (logged "POST /" for the 400, 401 and 403) and passes after; NV-167.</t>
+  </si>
+  <si>
+    <t>DEF-030</t>
+  </si>
+  <si>
+    <t>After sign-in the client stayed on the page the previous user had been on. A Requester signing in on the Management page was refused report:read, and the refusal was recorded (audit log, 15:48:36 and 15:51:38 UTC on 17/10/2026).</t>
+  </si>
+  <si>
+    <t>FR-1.3 (refused attempts recorded), DEC-012; client/src/permissions.js, client/src/auth.jsx</t>
+  </si>
+  <si>
+    <t>A user could land on a page their role may not use and see a refusal; spurious refusals were recorded.</t>
+  </si>
+  <si>
+    <t>After sign-in the user goes to their role's home page when a different person was last signed in in that tab or the page is not one of their own; an in-place sign-in on a request detail stays on that request.</t>
+  </si>
+  <si>
+    <t>E2E-10 step 1: a Requester signing in where a Manager was lands on My requests with no refusal: E2E run after the section A fixes, 09e6e6a, 17:17:57-17:20:59 UTC 17/10/2026: 44 of 44 in Chromium, Chrome, Edge and Firefox (docs/evidence/M4-build/E2E_run_2026-10-17_sectionA_four_browsers.txt).</t>
+  </si>
+  <si>
+    <t>DEF-031</t>
+  </si>
+  <si>
+    <t>E2E-11 (AC-FR-4.2), first development run in Chromium on task/M4-final-product, 18:10:34 UTC 17/10/2026</t>
+  </si>
+  <si>
+    <t>A request page opened signed out and then signed in on the page showed "Request" in place of the category name. The client loaded the category list once, when the page opened; that call was refused with 401 before the sign-in and was never made again.</t>
+  </si>
+  <si>
+    <t>FR-4.2, AC-FR-4.2; client/src/ui.jsx (useCategories), used by the request page and the request lists</t>
+  </si>
+  <si>
+    <t>A staff user who signed in on a request link (for example from a notification) could not see which category the request was in, one of the items AC-FR-4.2 requires on the request page.</t>
+  </si>
+  <si>
+    <t>The category list is loaded again whenever the signed-in user changes, so a sign-in on the page fetches it with the new session.</t>
+  </si>
+  <si>
+    <t>Commit 83c3b3f on task/M4-final-product</t>
+  </si>
+  <si>
+    <t>E2E-11 failed before the fix (heading "Request" where "facility faults" was expected; development run 18:10:34-18:11:05 UTC) and passed after it (18:12:00-18:12:20 UTC), Chromium only: docs/evidence/M4-build/E2E_dev_2026-10-17_E2E-11_to_13_run1_chromium.txt and _run2_chromium.txt. Four-browser run on 6408ab7, 18:57:36-19:01:25 UTC 17/10/2026: E2E-11 passed in Chromium, Chrome, Edge and Firefox, 56 of 56 (docs/evidence/M4-build/E2E_run_2026-10-17_final_four_browsers_run2.txt).</t>
+  </si>
+  <si>
+    <t>DEF-032</t>
+  </si>
+  <si>
+    <t>E. Lindsay, NFR-2.4 and NFR-2.1 runs on staging at v4.0-M4-rc, 18/10/2026 00:59 to 01:35 UTC</t>
+  </si>
+  <si>
+    <t>Concurrent request submissions contend on the single per-year reference counter inside the create transaction. Each submission increments the counter document request-ref:&lt;year&gt; (counterRepository.next, findOneAndUpdate $inc) inside unitOfWork.run (withTransaction, snapshot read concern, w majority). Concurrent submissions write the same document, conflict (WriteConflict, code 112, TransientTransactionError) and are re-run immediately by the driver until they win or 120 s pass; the last error then reaches the error handler as an unhandled 500.</t>
+  </si>
+  <si>
+    <t>FR-2.1, FR-2.6, NFR-2.1, AC-NFR-2.1, NFR-2.4, AC-NFR-2.4, DEC-016, RSK-019; src/repositories/counterRepository.js, src/services/requestSubmissionService.js, src/infrastructure/unitOfWork.js</t>
+  </si>
+  <si>
+    <t>Under concurrent submissions a requester's request can be lost, or saved without the requester being told. On staging, under 100 concurrent users (NFR-2.4), submissions reached p95 6.9 s and max 29.9 s server-side and 17 exceeded the client's 30 s limit (all saved). Under 100 simultaneous submissions (NFR-2.1), 70 were saved, 27 confirmed, 2 within 3 s, and 30 lost. A retry on the same form replays through the Idempotency-Key (DEC-015 §3); a reload, or an API client retrying with a new key, can create a duplicate.</t>
+  </si>
+  <si>
+    <t>Proposed, not built (the code is frozen for M4): allocate the reference outside the multi-document transaction (a single-document atomic $inc before it, accepting gaps, since FR-2.6 asks for unique and immutable, not gap-free; or allocate in blocks; or a counter per campus or shard); give the transaction a time budget below the proxy timeout and return a defined problem response (for example 503 with Retry-After) instead of an unhandled 500; add jittered backoff if contention remains; then re-run AC-NFR-2.1 and AC-NFR-2.4 on a colocated cluster.</t>
+  </si>
+  <si>
+    <t>None (not fixed in M4)</t>
+  </si>
+  <si>
+    <t>Found by the RC staging runs: docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md sections 7 and 8; docs/evidence/M4-perf/NFR-2.4_load_run_2026-10-18.txt; docs/evidence/M4-perf/NFR-2.1_submit_run_2026-10-18.txt. No regression test yet.</t>
+  </si>
+  <si>
+    <t>Blocks release to production (a go-live no-go reason). AC-NFR-2.1 and AC-NFR-2.4 are Not Met at the RC. Single-user use is unaffected (the RC walkthrough submitted normally, CC-2026-000521).</t>
+  </si>
+  <si>
+    <t>Limitation: under concurrent submissions, requests are delayed and some lost; AC-NFR-2.1 (2 of 100 within 3 s; 95 required) and AC-NFR-2.4 (17 failed requests) are Not Met at v4.0-M4-rc. Priority P2 (before M4), not achieved: the code was frozen for M4, so the fix is future work and a go-live condition. Evidence: docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md.</t>
+  </si>
+  <si>
+    <t>Fixed by #123</t>
+  </si>
+  <si>
+    <t>Ethan (register); Christiaan (fix)</t>
+  </si>
+  <si>
+    <t>M3 brief §12: "Maintain a simple defect record: defect -&gt; severity/impact -&gt; status -&gt; fix -&gt; regression evidence where corrected." §15: "Known defects | Open/closed | Business impact | Block or residual risk". Each row has a stable DEF identifier the RTM Defect/Status column can cite. Identifiers are never reused or renumbered; a closed defect stays in the register. | Version 0.6 (17/10/2026, M4 final pass, R. van der Merwe). Adds DEF-021 (staging did not serve the client until the Nginx site file was corrected on 15/10/2026; recorded at M3 only in the deploy record, and entered here so the register is complete), raised by E. Lindsay and allocated by R. van der Merwe. Adds columns P (Final status, M4: Fixed, Open or No longer relevant) and Q (the evidence, or the limitation and its consequence). DEF-006 is fixed by DEC-003 v0.5, and its J to M cells are completed. DEF-019's L and M cells cite PR #123. DEF-007 to DEF-012 were on E. Lindsay's M4 fix list; their J to Q cells were completed on 18/10/2026 from the v4.0-M4-rc evidence, and DEF-019 is closed (PR #123 is in the release candidate); its owner reads Ethan (register); Christiaan (fix), as #123 is C. Burger's. Adds DEF-022 to DEF-031 (M4 build and walkthrough, raised and allocated by E. Lindsay), each Fixed in PR #136, and DEF-032 (counter contention under concurrent submissions, found on staging at v4.0-M4-rc, 18/10/2026; S1, P2, Open). No other existing cell changes. Version 0.5 (15/10/2026). Adds DEF-019 (two test titles cite the wrong requirement), raised by E. Lindsay, and DEF-020 (the staging MONGODB_URI named no database, so the application used the default test database), raised by R. van der Merwe. Closes DEF-014, DEF-015 and DEF-017: their unique indexes were provisioned and confirmed on the test cluster (PR #102) and the staging cluster (PR #111); closure text by R. van der Merwe, entered by E. Lindsay. DEF-006 records the one-off drop of the test database on 14/10/2026. DEF-001 to DEF-005, DEF-007 to DEF-013, DEF-016 and DEF-018 unchanged. Version 0.4 (14/10/2026). Adds DEF-018 (an unexplained npm test failure in the PR #98 build: 3 failures, test names not captured), raised by R. van der Merwe. DEF-001 to DEF-017 unchanged. Version 0.3 (12/10/2026). Adds DEF-017 (the unique index on users.email is absent on the test cluster; FR-1.1 relies on it alone), raised by E. Lindsay; DEF-014 and DEF-015 cell E updated with the observed index absence from the test-cluster listing. DEF-001 to DEF-016 otherwise unchanged. Version 0.2 (12/10/2026). Adds DEF-005 to DEF-016: DEF-007 to DEF-010, DEF-014, and DEF-015 from M3 integration testing (R. van der Merwe); DEF-005, DEF-006, DEF-011 to DEF-013, and DEF-016 raised by E. Lindsay. DEF-001 to DEF-004 unchanged. Version 0.1 (11/10/2026). Register created with DEF-001 to DEF-004.</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:Q31"/>
+  <dimension ref="B1:Q42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -1194,7 +1467,7 @@
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>198</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
@@ -1614,13 +1887,13 @@
         <v>28</v>
       </c>
       <c r="K17" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="L17" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="L17" s="5" t="s">
+      <c r="M17" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>78</v>
@@ -1632,7 +1905,7 @@
         <v>179</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1665,13 +1938,13 @@
         <v>28</v>
       </c>
       <c r="K18" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="M18" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>204</v>
       </c>
       <c r="N18" s="5" t="s">
         <v>84</v>
@@ -1683,7 +1956,7 @@
         <v>179</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1716,13 +1989,13 @@
         <v>28</v>
       </c>
       <c r="K19" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="M19" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="N19" s="5" t="s">
         <v>90</v>
@@ -1734,7 +2007,7 @@
         <v>179</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1767,13 +2040,13 @@
         <v>28</v>
       </c>
       <c r="K20" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="M20" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>210</v>
       </c>
       <c r="N20" s="5" t="s">
         <v>95</v>
@@ -1785,7 +2058,7 @@
         <v>179</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1818,13 +2091,13 @@
         <v>28</v>
       </c>
       <c r="K21" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="M21" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>213</v>
       </c>
       <c r="N21" s="5" t="s">
         <v>100</v>
@@ -1836,7 +2109,7 @@
         <v>179</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1869,13 +2142,13 @@
         <v>28</v>
       </c>
       <c r="K22" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="L22" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="L22" s="5" t="s">
+      <c r="M22" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="N22" s="5" t="s">
         <v>105</v>
@@ -1887,7 +2160,7 @@
         <v>179</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2238,13 +2511,13 @@
         <v>148</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>33</v>
+        <v>309</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>179</v>
+        <v>308</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="2:17" ht="409.5" x14ac:dyDescent="0.25">
@@ -2348,8 +2621,569 @@
         <v>192</v>
       </c>
     </row>
+    <row r="32" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C32" s="4">
+        <f>DATE(2026,10,17)</f>
+        <v>46312</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q32" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C33" s="4">
+        <f>DATE(2026,10,17)</f>
+        <v>46312</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q33" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C34" s="4">
+        <f>DATE(2026,10,17)</f>
+        <v>46312</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q34" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C35" s="4">
+        <f>DATE(2026,10,17)</f>
+        <v>46312</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P35" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q35" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C36" s="4">
+        <f>DATE(2026,10,17)</f>
+        <v>46312</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P36" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q36" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C37" s="4">
+        <f>DATE(2026,10,17)</f>
+        <v>46312</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="N37" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="O37" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P37" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q37" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C38" s="4">
+        <f>DATE(2026,10,17)</f>
+        <v>46312</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P38" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q38" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C39" s="4">
+        <f>DATE(2026,10,17)</f>
+        <v>46312</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q39" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C40" s="4">
+        <f>DATE(2026,10,17)</f>
+        <v>46312</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q40" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C41" s="4">
+        <f>DATE(2026,10,17)</f>
+        <v>46312</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="N41" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q41" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C42" s="4">
+        <f>DATE(2026,10,18)</f>
+        <v>46313</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q42" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B10:Q31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="B10:Q42" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/quality/Defect Register/Defect Register v0.6.xlsx
+++ b/docs/quality/Defect Register/Defect Register v0.6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\SEN381\Repo\Ticketing-System\docs\quality\Defect Register\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443AE430-7E4E-4CF1-93E8-960089DFF339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065DA4EE-0551-4849-B236-DEAA98020CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="310">
   <si>
     <t>Defect Register</t>
   </si>
@@ -584,9 +584,6 @@
     <t>Regression test tests/openapiContract.test.js, with negative verifications NV-25 and NV-26. From PR #123 (TD-007) the test reads the parsed YAML, not regular expressions, so a broken file can no longer pass it.</t>
   </si>
   <si>
-    <t>Near miss, never committed. The full-history secret scan has passed on every pull request since, including the 104 CI runs from 13/10/2026 to 17/10/2026.</t>
-  </si>
-  <si>
     <t>Documentation corrected (c1514d0). The recorded staging smoke run used the explicit HTTPS address, not localhost (PR #111).</t>
   </si>
   <si>
@@ -962,13 +959,13 @@
     <t>Limitation: under concurrent submissions, requests are delayed and some lost; AC-NFR-2.1 (2 of 100 within 3 s; 95 required) and AC-NFR-2.4 (17 failed requests) are Not Met at v4.0-M4-rc. Priority P2 (before M4), not achieved: the code was frozen for M4, so the fix is future work and a go-live condition. Evidence: docs/evidence/M4_Staging_Deploy_v4.0-M4-rc.md.</t>
   </si>
   <si>
-    <t>Fixed by #123</t>
-  </si>
-  <si>
     <t>Ethan (register); Christiaan (fix)</t>
   </si>
   <si>
-    <t>M3 brief §12: "Maintain a simple defect record: defect -&gt; severity/impact -&gt; status -&gt; fix -&gt; regression evidence where corrected." §15: "Known defects | Open/closed | Business impact | Block or residual risk". Each row has a stable DEF identifier the RTM Defect/Status column can cite. Identifiers are never reused or renumbered; a closed defect stays in the register. | Version 0.6 (17/10/2026, M4 final pass, R. van der Merwe). Adds DEF-021 (staging did not serve the client until the Nginx site file was corrected on 15/10/2026; recorded at M3 only in the deploy record, and entered here so the register is complete), raised by E. Lindsay and allocated by R. van der Merwe. Adds columns P (Final status, M4: Fixed, Open or No longer relevant) and Q (the evidence, or the limitation and its consequence). DEF-006 is fixed by DEC-003 v0.5, and its J to M cells are completed. DEF-019's L and M cells cite PR #123. DEF-007 to DEF-012 were on E. Lindsay's M4 fix list; their J to Q cells were completed on 18/10/2026 from the v4.0-M4-rc evidence, and DEF-019 is closed (PR #123 is in the release candidate); its owner reads Ethan (register); Christiaan (fix), as #123 is C. Burger's. Adds DEF-022 to DEF-031 (M4 build and walkthrough, raised and allocated by E. Lindsay), each Fixed in PR #136, and DEF-032 (counter contention under concurrent submissions, found on staging at v4.0-M4-rc, 18/10/2026; S1, P2, Open). No other existing cell changes. Version 0.5 (15/10/2026). Adds DEF-019 (two test titles cite the wrong requirement), raised by E. Lindsay, and DEF-020 (the staging MONGODB_URI named no database, so the application used the default test database), raised by R. van der Merwe. Closes DEF-014, DEF-015 and DEF-017: their unique indexes were provisioned and confirmed on the test cluster (PR #102) and the staging cluster (PR #111); closure text by R. van der Merwe, entered by E. Lindsay. DEF-006 records the one-off drop of the test database on 14/10/2026. DEF-001 to DEF-005, DEF-007 to DEF-013, DEF-016 and DEF-018 unchanged. Version 0.4 (14/10/2026). Adds DEF-018 (an unexplained npm test failure in the PR #98 build: 3 failures, test names not captured), raised by R. van der Merwe. DEF-001 to DEF-017 unchanged. Version 0.3 (12/10/2026). Adds DEF-017 (the unique index on users.email is absent on the test cluster; FR-1.1 relies on it alone), raised by E. Lindsay; DEF-014 and DEF-015 cell E updated with the observed index absence from the test-cluster listing. DEF-001 to DEF-016 otherwise unchanged. Version 0.2 (12/10/2026). Adds DEF-005 to DEF-016: DEF-007 to DEF-010, DEF-014, and DEF-015 from M3 integration testing (R. van der Merwe); DEF-005, DEF-006, DEF-011 to DEF-013, and DEF-016 raised by E. Lindsay. DEF-001 to DEF-004 unchanged. Version 0.1 (11/10/2026). Register created with DEF-001 to DEF-004.</t>
+    <t>Near miss, never committed. No credential has been committed since. The full-history secret scan failed in eight CI runs between 11/10/2026 and 18/10/2026, and none was a credential. Seven reported findings: SHA-256 hash lines in negative-verification records (docs/evidence/M3-client NV-55, NV-60 and NV-61 on PR #89, also caught on 13/10/2026 in the GATE-01 demonstration run and on task/update-dec-003; the TD-007 record on PR #123, ignored in 404a471), and a synthetic test password in tests/userInitialPassword.test.js on PR #136 (now assembled at run time, ddd36af). Each was ignored by fingerprint in .gitleaksignore after review. The eighth (12/10/2026, task/M3-ci-quality-gates) reported no leaks and failed for another reason.</t>
+  </si>
+  <si>
+    <t>M3 brief §12: "Maintain a simple defect record: defect -&gt; severity/impact -&gt; status -&gt; fix -&gt; regression evidence where corrected." §15: "Known defects | Open/closed | Business impact | Block or residual risk". Each row has a stable DEF identifier the RTM Defect/Status column can cite. Identifiers are never reused or renumbered; a closed defect stays in the register. | Version 0.6 (17/10/2026, M4 final pass, R. van der Merwe). Adds DEF-021 (staging did not serve the client until the Nginx site file was corrected on 15/10/2026; recorded at M3 only in the deploy record, and entered here so the register is complete), raised by E. Lindsay and allocated by R. van der Merwe. Adds columns P (Final status, M4: Fixed, Open or No longer relevant) and Q (the evidence, or the limitation and its consequence). DEF-006 is fixed by DEC-003 v0.5, and its J to M cells are completed. DEF-019's L and M cells cite PR #123. DEF-007 to DEF-012 were on E. Lindsay's M4 fix list; their J to Q cells were completed on 18/10/2026 from the v4.0-M4-rc evidence, and DEF-019 is closed (PR #123 is in the release candidate); its owner reads Ethan (register); Christiaan (fix), as #123 is C. Burger's. Adds DEF-022 to DEF-031 (M4 build and walkthrough, raised and allocated by E. Lindsay), each Fixed in PR #136, and DEF-032 (counter contention under concurrent submissions, found on staging at v4.0-M4-rc, 18/10/2026; S1, P2, Open). No other existing cell changes. After review (18/10/2026): Q13 (DEF-003) states the secret scan's failures accurately, P29 reads Fixed so the filter groups it, and C31 is entered as a DATE formula like the other rows. Version 0.5 (15/10/2026). Adds DEF-019 (two test titles cite the wrong requirement), raised by E. Lindsay, and DEF-020 (the staging MONGODB_URI named no database, so the application used the default test database), raised by R. van der Merwe. Closes DEF-014, DEF-015 and DEF-017: their unique indexes were provisioned and confirmed on the test cluster (PR #102) and the staging cluster (PR #111); closure text by R. van der Merwe, entered by E. Lindsay. DEF-006 records the one-off drop of the test database on 14/10/2026. DEF-001 to DEF-005, DEF-007 to DEF-013, DEF-016 and DEF-018 unchanged. Version 0.4 (14/10/2026). Adds DEF-018 (an unexplained npm test failure in the PR #98 build: 3 failures, test names not captured), raised by R. van der Merwe. DEF-001 to DEF-017 unchanged. Version 0.3 (12/10/2026). Adds DEF-017 (the unique index on users.email is absent on the test cluster; FR-1.1 relies on it alone), raised by E. Lindsay; DEF-014 and DEF-015 cell E updated with the observed index absence from the test-cluster listing. DEF-001 to DEF-016 otherwise unchanged. Version 0.2 (12/10/2026). Adds DEF-005 to DEF-016: DEF-007 to DEF-010, DEF-014, and DEF-015 from M3 integration testing (R. van der Merwe); DEF-005, DEF-006, DEF-011 to DEF-013, and DEF-016 raised by E. Lindsay. DEF-001 to DEF-004 unchanged. Version 0.1 (11/10/2026). Register created with DEF-001 to DEF-004.</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1464,7 @@
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
@@ -1701,7 +1698,7 @@
         <v>179</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>182</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1752,7 +1749,7 @@
         <v>179</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1803,7 +1800,7 @@
         <v>66</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1836,13 +1833,13 @@
         <v>28</v>
       </c>
       <c r="K16" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="L16" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="L16" s="5" t="s">
+      <c r="M16" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="N16" s="5" t="s">
         <v>72</v>
@@ -1854,7 +1851,7 @@
         <v>179</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1887,13 +1884,13 @@
         <v>28</v>
       </c>
       <c r="K17" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="L17" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L17" s="5" t="s">
+      <c r="M17" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>78</v>
@@ -1905,7 +1902,7 @@
         <v>179</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1938,13 +1935,13 @@
         <v>28</v>
       </c>
       <c r="K18" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="M18" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="N18" s="5" t="s">
         <v>84</v>
@@ -1956,7 +1953,7 @@
         <v>179</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1989,13 +1986,13 @@
         <v>28</v>
       </c>
       <c r="K19" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="M19" s="5" t="s">
         <v>205</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="N19" s="5" t="s">
         <v>90</v>
@@ -2007,7 +2004,7 @@
         <v>179</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2040,13 +2037,13 @@
         <v>28</v>
       </c>
       <c r="K20" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="M20" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="M20" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="N20" s="5" t="s">
         <v>95</v>
@@ -2058,7 +2055,7 @@
         <v>179</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2091,13 +2088,13 @@
         <v>28</v>
       </c>
       <c r="K21" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="M21" s="5" t="s">
         <v>211</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>212</v>
       </c>
       <c r="N21" s="5" t="s">
         <v>100</v>
@@ -2109,7 +2106,7 @@
         <v>179</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2142,13 +2139,13 @@
         <v>28</v>
       </c>
       <c r="K22" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="L22" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="L22" s="5" t="s">
+      <c r="M22" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>216</v>
       </c>
       <c r="N22" s="5" t="s">
         <v>105</v>
@@ -2160,7 +2157,7 @@
         <v>179</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2211,7 +2208,7 @@
         <v>66</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2262,7 +2259,7 @@
         <v>179</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2313,7 +2310,7 @@
         <v>179</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="2:17" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2364,7 +2361,7 @@
         <v>66</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="2:17" ht="174" customHeight="1" x14ac:dyDescent="0.25">
@@ -2415,7 +2412,7 @@
         <v>179</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="2:17" ht="174" customHeight="1" x14ac:dyDescent="0.25">
@@ -2466,7 +2463,7 @@
         <v>66</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="2:17" ht="174" customHeight="1" x14ac:dyDescent="0.25">
@@ -2502,22 +2499,22 @@
         <v>147</v>
       </c>
       <c r="L29" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="M29" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="M29" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>148</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>308</v>
+        <v>179</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="2:17" ht="409.5" x14ac:dyDescent="0.25">
@@ -2568,7 +2565,7 @@
         <v>179</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2576,6 +2573,7 @@
         <v>167</v>
       </c>
       <c r="C31" s="4">
+        <f>DATE(2026,10,17)</f>
         <v>46312</v>
       </c>
       <c r="D31" s="5" t="s">
@@ -2618,31 +2616,31 @@
         <v>179</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C32" s="4">
+        <f t="shared" ref="C32:C41" si="1">DATE(2026,10,17)</f>
+        <v>46312</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C32" s="4">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="F32" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>65</v>
@@ -2651,16 +2649,16 @@
         <v>28</v>
       </c>
       <c r="K32" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="M32" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="M32" s="6" t="s">
+      <c r="N32" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="N32" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>33</v>
@@ -2669,31 +2667,31 @@
         <v>179</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C33" s="4">
+        <f t="shared" si="1"/>
+        <v>46312</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="C33" s="4">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="D33" s="5" t="s">
+      <c r="E33" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="F33" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>65</v>
@@ -2702,16 +2700,16 @@
         <v>28</v>
       </c>
       <c r="K33" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="L33" s="6" t="s">
+      <c r="M33" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="M33" s="6" t="s">
+      <c r="N33" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="N33" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>33</v>
@@ -2720,31 +2718,31 @@
         <v>179</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="34" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C34" s="4">
+        <f t="shared" si="1"/>
+        <v>46312</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="C34" s="4">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="D34" s="5" t="s">
+      <c r="E34" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="F34" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="G34" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>243</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>65</v>
@@ -2753,16 +2751,16 @@
         <v>28</v>
       </c>
       <c r="K34" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="L34" s="6" t="s">
+      <c r="M34" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="M34" s="6" t="s">
+      <c r="N34" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="N34" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>33</v>
@@ -2771,31 +2769,31 @@
         <v>179</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="35" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C35" s="4">
+        <f t="shared" si="1"/>
+        <v>46312</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="C35" s="4">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E35" s="6" t="s">
+      <c r="F35" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>88</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>65</v>
@@ -2804,16 +2802,16 @@
         <v>28</v>
       </c>
       <c r="K35" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="L35" s="6" t="s">
+      <c r="M35" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="M35" s="6" t="s">
-        <v>256</v>
-      </c>
       <c r="N35" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>33</v>
@@ -2822,31 +2820,31 @@
         <v>179</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C36" s="4">
+        <f t="shared" si="1"/>
+        <v>46312</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="C36" s="4">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E36" s="6" t="s">
+      <c r="F36" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>65</v>
@@ -2855,16 +2853,16 @@
         <v>28</v>
       </c>
       <c r="K36" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="M36" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="L36" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>262</v>
-      </c>
       <c r="N36" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>33</v>
@@ -2873,31 +2871,31 @@
         <v>179</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="37" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C37" s="4">
+        <f t="shared" si="1"/>
+        <v>46312</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C37" s="4">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E37" s="6" t="s">
+      <c r="F37" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>65</v>
@@ -2906,16 +2904,16 @@
         <v>28</v>
       </c>
       <c r="K37" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="L37" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="L37" s="6" t="s">
+      <c r="M37" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="M37" s="6" t="s">
+      <c r="N37" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="N37" s="6" t="s">
-        <v>270</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>33</v>
@@ -2924,31 +2922,31 @@
         <v>179</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C38" s="4">
+        <f t="shared" si="1"/>
+        <v>46312</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="C38" s="4">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E38" s="6" t="s">
+      <c r="F38" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>273</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>65</v>
@@ -2957,16 +2955,16 @@
         <v>28</v>
       </c>
       <c r="K38" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="M38" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="L38" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="M38" s="6" t="s">
-        <v>276</v>
-      </c>
       <c r="N38" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>33</v>
@@ -2975,31 +2973,31 @@
         <v>179</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="39" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C39" s="4">
+        <f t="shared" si="1"/>
+        <v>46312</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="C39" s="4">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E39" s="6" t="s">
+      <c r="F39" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>279</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I39" s="6" t="s">
         <v>65</v>
@@ -3008,16 +3006,16 @@
         <v>28</v>
       </c>
       <c r="K39" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="L39" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="L39" s="6" t="s">
+      <c r="M39" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="M39" s="6" t="s">
-        <v>283</v>
-      </c>
       <c r="N39" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>33</v>
@@ -3026,31 +3024,31 @@
         <v>179</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="40" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C40" s="4">
+        <f t="shared" si="1"/>
+        <v>46312</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="C40" s="4">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E40" s="6" t="s">
+      <c r="F40" s="6" t="s">
         <v>285</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>286</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>65</v>
@@ -3059,16 +3057,16 @@
         <v>28</v>
       </c>
       <c r="K40" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="M40" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="L40" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="M40" s="6" t="s">
-        <v>289</v>
-      </c>
       <c r="N40" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>33</v>
@@ -3077,31 +3075,31 @@
         <v>179</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C41" s="4">
+        <f t="shared" si="1"/>
+        <v>46312</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="C41" s="4">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="D41" s="5" t="s">
+      <c r="E41" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="F41" s="6" t="s">
         <v>292</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>293</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I41" s="6" t="s">
         <v>65</v>
@@ -3110,16 +3108,16 @@
         <v>28</v>
       </c>
       <c r="K41" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="L41" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="L41" s="6" t="s">
+      <c r="M41" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="M41" s="6" t="s">
-        <v>297</v>
-      </c>
       <c r="N41" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>33</v>
@@ -3128,31 +3126,31 @@
         <v>179</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="42" spans="2:17" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C42" s="4">
         <f>DATE(2026,10,18)</f>
         <v>46313</v>
       </c>
       <c r="D42" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="G42" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>301</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>302</v>
       </c>
       <c r="I42" s="6" t="s">
         <v>65</v>
@@ -3161,16 +3159,16 @@
         <v>66</v>
       </c>
       <c r="K42" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="L42" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="L42" s="6" t="s">
+      <c r="M42" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="M42" s="6" t="s">
+      <c r="N42" s="6" t="s">
         <v>305</v>
-      </c>
-      <c r="N42" s="6" t="s">
-        <v>306</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>33</v>
@@ -3179,7 +3177,7 @@
         <v>66</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
